--- a/SISTEM KEBERADAAN MURID ASRAMA (V2).xlsx
+++ b/SISTEM KEBERADAAN MURID ASRAMA (V2).xlsx
@@ -7,6 +7,8 @@
     <sheet state="visible" name="Logs" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="Pending" sheetId="3" r:id="rId7"/>
     <sheet state="visible" name="MeritLogs" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="SenaraiKelas" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="SenaraiNamaBilik" sheetId="6" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -14,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="192">
   <si>
     <t>Nama Murid</t>
   </si>
@@ -52,10 +54,10 @@
     <t>PEREMPUAN</t>
   </si>
   <si>
-    <t>Keluar</t>
+    <t>Masuk</t>
   </si>
   <si>
-    <t>Balik Kampung</t>
+    <t>-</t>
   </si>
   <si>
     <t>PENYEL A/P UDA</t>
@@ -502,6 +504,12 @@
     <t>Gambar</t>
   </si>
   <si>
+    <t>Keluar</t>
+  </si>
+  <si>
+    <t>Balik Kampung</t>
+  </si>
+  <si>
     <t>ID</t>
   </si>
   <si>
@@ -535,10 +543,10 @@
     <t>Merit</t>
   </si>
   <si>
-    <t>Ponteng</t>
+    <t>Tolong cikgu</t>
   </si>
   <si>
-    <t>https://drive.google.com/thumbnail?id=193xiejYGv56a5FxyAudurWiCLf55OGgO&amp;sz=w800</t>
+    <t>https://drive.google.com/thumbnail?id=1vesP3l6F4JJdZFy47wfHG8x0hGqMbk3m&amp;sz=w800</t>
   </si>
   <si>
     <t>warden1</t>
@@ -547,22 +555,43 @@
     <t>Demerit</t>
   </si>
   <si>
-    <t>Bising</t>
+    <t>Bising waktu tidur</t>
   </si>
   <si>
-    <t>https://drive.google.com/thumbnail?id=1vviwW41oMmPbtapV1W8VEO7QKoMu7_3p&amp;sz=w800</t>
+    <t>KELAS</t>
   </si>
   <si>
-    <t>Tolong cikgu</t>
+    <t xml:space="preserve">1 NILAM </t>
   </si>
   <si>
-    <t>https://drive.google.com/thumbnail?id=1DLt8vmLJKw5BJrdzMgxyPjKxlRVUoJbv&amp;sz=w800</t>
+    <t>1 ZAMRUD</t>
   </si>
   <si>
-    <t>Tolong saya</t>
+    <t xml:space="preserve">2 NILAM </t>
   </si>
   <si>
-    <t>https://drive.google.com/thumbnail?id=1SzRn_g01d_EzSSyRXwhzbFWzTVaSYYE3&amp;sz=w800</t>
+    <t>2 ZAMRUD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 NILAM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 MUTIARA </t>
+  </si>
+  <si>
+    <t>3 ZAMRUD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 DELIMA </t>
+  </si>
+  <si>
+    <t>4 ZAMRUD</t>
+  </si>
+  <si>
+    <t>Nama Bilik</t>
+  </si>
+  <si>
+    <t>FLORA (P</t>
   </si>
 </sst>
 </file>
@@ -738,6 +767,14 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -1014,14 +1051,14 @@
         <v>12</v>
       </c>
       <c r="F2" s="8">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="10">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -1059,14 +1096,14 @@
         <v>12</v>
       </c>
       <c r="F3" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>13</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="10">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
@@ -1104,15 +1141,13 @@
         <v>12</v>
       </c>
       <c r="F4" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>13</v>
       </c>
       <c r="H4" s="6"/>
-      <c r="I4" s="10">
-        <v>10.0</v>
-      </c>
+      <c r="I4" s="10"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
@@ -1149,7 +1184,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>13</v>
@@ -1192,7 +1227,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>13</v>
@@ -1235,7 +1270,7 @@
         <v>12</v>
       </c>
       <c r="F7" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>13</v>
@@ -1278,7 +1313,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>13</v>
@@ -1321,7 +1356,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>13</v>
@@ -1364,7 +1399,7 @@
         <v>12</v>
       </c>
       <c r="F10" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>13</v>
@@ -1407,7 +1442,7 @@
         <v>12</v>
       </c>
       <c r="F11" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>13</v>
@@ -1450,7 +1485,7 @@
         <v>12</v>
       </c>
       <c r="F12" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>13</v>
@@ -1493,7 +1528,7 @@
         <v>12</v>
       </c>
       <c r="F13" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>13</v>
@@ -1536,7 +1571,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>13</v>
@@ -1579,7 +1614,7 @@
         <v>12</v>
       </c>
       <c r="F15" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>13</v>
@@ -1622,7 +1657,7 @@
         <v>12</v>
       </c>
       <c r="F16" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>13</v>
@@ -1665,7 +1700,7 @@
         <v>12</v>
       </c>
       <c r="F17" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>13</v>
@@ -1708,7 +1743,7 @@
         <v>12</v>
       </c>
       <c r="F18" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>13</v>
@@ -1751,7 +1786,7 @@
         <v>12</v>
       </c>
       <c r="F19" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>13</v>
@@ -1794,7 +1829,7 @@
         <v>12</v>
       </c>
       <c r="F20" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>13</v>
@@ -1837,7 +1872,7 @@
         <v>12</v>
       </c>
       <c r="F21" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>13</v>
@@ -1880,15 +1915,13 @@
         <v>12</v>
       </c>
       <c r="F22" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>13</v>
       </c>
       <c r="H22" s="13"/>
-      <c r="I22" s="10">
-        <v>5.0</v>
-      </c>
+      <c r="I22" s="10"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
@@ -1925,7 +1958,7 @@
         <v>12</v>
       </c>
       <c r="F23" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>13</v>
@@ -1968,7 +2001,7 @@
         <v>12</v>
       </c>
       <c r="F24" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>13</v>
@@ -2011,7 +2044,7 @@
         <v>12</v>
       </c>
       <c r="F25" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>13</v>
@@ -2054,7 +2087,7 @@
         <v>12</v>
       </c>
       <c r="F26" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>13</v>
@@ -2097,7 +2130,7 @@
         <v>12</v>
       </c>
       <c r="F27" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>13</v>
@@ -2140,7 +2173,7 @@
         <v>12</v>
       </c>
       <c r="F28" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>13</v>
@@ -2183,7 +2216,7 @@
         <v>12</v>
       </c>
       <c r="F29" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>13</v>
@@ -2226,7 +2259,7 @@
         <v>12</v>
       </c>
       <c r="F30" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>13</v>
@@ -2269,15 +2302,13 @@
         <v>12</v>
       </c>
       <c r="F31" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>13</v>
       </c>
       <c r="H31" s="13"/>
-      <c r="I31" s="10">
-        <v>5.0</v>
-      </c>
+      <c r="I31" s="10"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
@@ -2314,7 +2345,7 @@
         <v>12</v>
       </c>
       <c r="F32" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>13</v>
@@ -2357,15 +2388,13 @@
         <v>12</v>
       </c>
       <c r="F33" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>13</v>
       </c>
       <c r="H33" s="13"/>
-      <c r="I33" s="10">
-        <v>5.0</v>
-      </c>
+      <c r="I33" s="10"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
@@ -2402,7 +2431,7 @@
         <v>12</v>
       </c>
       <c r="F34" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>13</v>
@@ -2445,7 +2474,7 @@
         <v>12</v>
       </c>
       <c r="F35" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>13</v>
@@ -2488,15 +2517,13 @@
         <v>12</v>
       </c>
       <c r="F36" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>13</v>
       </c>
       <c r="H36" s="13"/>
-      <c r="I36" s="10">
-        <v>5.0</v>
-      </c>
+      <c r="I36" s="10"/>
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
@@ -2533,7 +2560,7 @@
         <v>12</v>
       </c>
       <c r="F37" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>13</v>
@@ -2576,7 +2603,7 @@
         <v>12</v>
       </c>
       <c r="F38" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>13</v>
@@ -2619,15 +2646,13 @@
         <v>12</v>
       </c>
       <c r="F39" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>13</v>
       </c>
       <c r="H39" s="13"/>
-      <c r="I39" s="10">
-        <v>7.0</v>
-      </c>
+      <c r="I39" s="10"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
@@ -2664,7 +2689,7 @@
         <v>12</v>
       </c>
       <c r="F40" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>13</v>
@@ -2707,7 +2732,7 @@
         <v>12</v>
       </c>
       <c r="F41" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>13</v>
@@ -2750,7 +2775,7 @@
         <v>12</v>
       </c>
       <c r="F42" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>13</v>
@@ -2793,7 +2818,7 @@
         <v>12</v>
       </c>
       <c r="F43" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>13</v>
@@ -2836,7 +2861,7 @@
         <v>12</v>
       </c>
       <c r="F44" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>13</v>
@@ -2879,7 +2904,7 @@
         <v>12</v>
       </c>
       <c r="F45" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>13</v>
@@ -2922,7 +2947,7 @@
         <v>12</v>
       </c>
       <c r="F46" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>13</v>
@@ -2965,7 +2990,7 @@
         <v>12</v>
       </c>
       <c r="F47" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>13</v>
@@ -3008,7 +3033,7 @@
         <v>12</v>
       </c>
       <c r="F48" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>13</v>
@@ -3051,7 +3076,7 @@
         <v>12</v>
       </c>
       <c r="F49" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>13</v>
@@ -3094,7 +3119,7 @@
         <v>12</v>
       </c>
       <c r="F50" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>13</v>
@@ -3137,7 +3162,7 @@
         <v>12</v>
       </c>
       <c r="F51" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>13</v>
@@ -3180,7 +3205,7 @@
         <v>12</v>
       </c>
       <c r="F52" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>13</v>
@@ -3223,7 +3248,7 @@
         <v>12</v>
       </c>
       <c r="F53" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>13</v>
@@ -3266,7 +3291,7 @@
         <v>12</v>
       </c>
       <c r="F54" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>13</v>
@@ -3309,7 +3334,7 @@
         <v>12</v>
       </c>
       <c r="F55" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>13</v>
@@ -3352,15 +3377,13 @@
         <v>12</v>
       </c>
       <c r="F56" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>13</v>
       </c>
       <c r="H56" s="13"/>
-      <c r="I56" s="10">
-        <v>5.0</v>
-      </c>
+      <c r="I56" s="10"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
@@ -3397,7 +3420,7 @@
         <v>12</v>
       </c>
       <c r="F57" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>13</v>
@@ -3440,7 +3463,7 @@
         <v>12</v>
       </c>
       <c r="F58" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>13</v>
@@ -3483,7 +3506,7 @@
         <v>12</v>
       </c>
       <c r="F59" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>13</v>
@@ -3526,7 +3549,7 @@
         <v>12</v>
       </c>
       <c r="F60" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>13</v>
@@ -3569,7 +3592,7 @@
         <v>12</v>
       </c>
       <c r="F61" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>13</v>
@@ -3612,7 +3635,7 @@
         <v>12</v>
       </c>
       <c r="F62" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>13</v>
@@ -3655,7 +3678,7 @@
         <v>12</v>
       </c>
       <c r="F63" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>13</v>
@@ -3698,7 +3721,7 @@
         <v>12</v>
       </c>
       <c r="F64" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>13</v>
@@ -3741,7 +3764,7 @@
         <v>12</v>
       </c>
       <c r="F65" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>13</v>
@@ -3784,7 +3807,7 @@
         <v>12</v>
       </c>
       <c r="F66" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G66" s="6" t="s">
         <v>13</v>
@@ -3827,7 +3850,7 @@
         <v>12</v>
       </c>
       <c r="F67" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G67" s="6" t="s">
         <v>13</v>
@@ -3870,7 +3893,7 @@
         <v>12</v>
       </c>
       <c r="F68" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G68" s="6" t="s">
         <v>13</v>
@@ -3913,7 +3936,7 @@
         <v>12</v>
       </c>
       <c r="F69" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G69" s="6" t="s">
         <v>13</v>
@@ -3956,7 +3979,7 @@
         <v>12</v>
       </c>
       <c r="F70" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G70" s="6" t="s">
         <v>13</v>
@@ -3999,15 +4022,13 @@
         <v>12</v>
       </c>
       <c r="F71" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G71" s="6" t="s">
         <v>13</v>
       </c>
       <c r="H71" s="13"/>
-      <c r="I71" s="10">
-        <v>5.0</v>
-      </c>
+      <c r="I71" s="10"/>
       <c r="J71" s="3"/>
       <c r="K71" s="3"/>
       <c r="L71" s="3"/>
@@ -4044,7 +4065,7 @@
         <v>12</v>
       </c>
       <c r="F72" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G72" s="6" t="s">
         <v>13</v>
@@ -4087,7 +4108,7 @@
         <v>12</v>
       </c>
       <c r="F73" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G73" s="6" t="s">
         <v>13</v>
@@ -4130,7 +4151,7 @@
         <v>12</v>
       </c>
       <c r="F74" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>13</v>
@@ -4173,7 +4194,7 @@
         <v>12</v>
       </c>
       <c r="F75" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>13</v>
@@ -4216,15 +4237,13 @@
         <v>12</v>
       </c>
       <c r="F76" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G76" s="6" t="s">
         <v>13</v>
       </c>
       <c r="H76" s="13"/>
-      <c r="I76" s="10">
-        <v>5.0</v>
-      </c>
+      <c r="I76" s="10"/>
       <c r="J76" s="3"/>
       <c r="K76" s="3"/>
       <c r="L76" s="3"/>
@@ -4261,7 +4280,7 @@
         <v>12</v>
       </c>
       <c r="F77" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G77" s="6" t="s">
         <v>13</v>
@@ -4304,7 +4323,7 @@
         <v>12</v>
       </c>
       <c r="F78" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>13</v>
@@ -4347,7 +4366,7 @@
         <v>12</v>
       </c>
       <c r="F79" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G79" s="6" t="s">
         <v>13</v>
@@ -4390,7 +4409,7 @@
         <v>12</v>
       </c>
       <c r="F80" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G80" s="6" t="s">
         <v>13</v>
@@ -4433,7 +4452,7 @@
         <v>12</v>
       </c>
       <c r="F81" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G81" s="6" t="s">
         <v>13</v>
@@ -4476,7 +4495,7 @@
         <v>12</v>
       </c>
       <c r="F82" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G82" s="6" t="s">
         <v>13</v>
@@ -4519,7 +4538,7 @@
         <v>12</v>
       </c>
       <c r="F83" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G83" s="6" t="s">
         <v>13</v>
@@ -4562,7 +4581,7 @@
         <v>12</v>
       </c>
       <c r="F84" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G84" s="6" t="s">
         <v>13</v>
@@ -4605,7 +4624,7 @@
         <v>12</v>
       </c>
       <c r="F85" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G85" s="6" t="s">
         <v>13</v>
@@ -4648,7 +4667,7 @@
         <v>12</v>
       </c>
       <c r="F86" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G86" s="6" t="s">
         <v>13</v>
@@ -4691,7 +4710,7 @@
         <v>12</v>
       </c>
       <c r="F87" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G87" s="6" t="s">
         <v>13</v>
@@ -4734,7 +4753,7 @@
         <v>12</v>
       </c>
       <c r="F88" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G88" s="6" t="s">
         <v>13</v>
@@ -4777,7 +4796,7 @@
         <v>12</v>
       </c>
       <c r="F89" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G89" s="6" t="s">
         <v>13</v>
@@ -4820,7 +4839,7 @@
         <v>12</v>
       </c>
       <c r="F90" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G90" s="6" t="s">
         <v>13</v>
@@ -4863,7 +4882,7 @@
         <v>12</v>
       </c>
       <c r="F91" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G91" s="6" t="s">
         <v>13</v>
@@ -4906,7 +4925,7 @@
         <v>12</v>
       </c>
       <c r="F92" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G92" s="6" t="s">
         <v>13</v>
@@ -4949,7 +4968,7 @@
         <v>12</v>
       </c>
       <c r="F93" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G93" s="6" t="s">
         <v>13</v>
@@ -4992,7 +5011,7 @@
         <v>12</v>
       </c>
       <c r="F94" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G94" s="6" t="s">
         <v>13</v>
@@ -5035,7 +5054,7 @@
         <v>12</v>
       </c>
       <c r="F95" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G95" s="6" t="s">
         <v>13</v>
@@ -5078,7 +5097,7 @@
         <v>12</v>
       </c>
       <c r="F96" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G96" s="6" t="s">
         <v>13</v>
@@ -5121,7 +5140,7 @@
         <v>12</v>
       </c>
       <c r="F97" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G97" s="6" t="s">
         <v>13</v>
@@ -5164,7 +5183,7 @@
         <v>12</v>
       </c>
       <c r="F98" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G98" s="6" t="s">
         <v>13</v>
@@ -5207,7 +5226,7 @@
         <v>12</v>
       </c>
       <c r="F99" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G99" s="6" t="s">
         <v>13</v>
@@ -5250,7 +5269,7 @@
         <v>12</v>
       </c>
       <c r="F100" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G100" s="6" t="s">
         <v>13</v>
@@ -5293,7 +5312,7 @@
         <v>12</v>
       </c>
       <c r="F101" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G101" s="6" t="s">
         <v>13</v>
@@ -5336,15 +5355,13 @@
         <v>12</v>
       </c>
       <c r="F102" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G102" s="6" t="s">
         <v>13</v>
       </c>
       <c r="H102" s="13"/>
-      <c r="I102" s="10">
-        <v>5.0</v>
-      </c>
+      <c r="I102" s="10"/>
       <c r="J102" s="3"/>
       <c r="K102" s="3"/>
       <c r="L102" s="3"/>
@@ -5381,15 +5398,13 @@
         <v>12</v>
       </c>
       <c r="F103" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G103" s="6" t="s">
         <v>13</v>
       </c>
       <c r="H103" s="13"/>
-      <c r="I103" s="10">
-        <v>5.0</v>
-      </c>
+      <c r="I103" s="10"/>
       <c r="J103" s="3"/>
       <c r="K103" s="3"/>
       <c r="L103" s="3"/>
@@ -5426,7 +5441,7 @@
         <v>12</v>
       </c>
       <c r="F104" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G104" s="6" t="s">
         <v>13</v>
@@ -5469,7 +5484,7 @@
         <v>12</v>
       </c>
       <c r="F105" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G105" s="6" t="s">
         <v>13</v>
@@ -5512,15 +5527,13 @@
         <v>12</v>
       </c>
       <c r="F106" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G106" s="6" t="s">
         <v>13</v>
       </c>
       <c r="H106" s="13"/>
-      <c r="I106" s="10">
-        <v>5.0</v>
-      </c>
+      <c r="I106" s="10"/>
       <c r="J106" s="3"/>
       <c r="K106" s="3"/>
       <c r="L106" s="3"/>
@@ -5557,7 +5570,7 @@
         <v>12</v>
       </c>
       <c r="F107" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G107" s="6" t="s">
         <v>13</v>
@@ -5600,7 +5613,7 @@
         <v>12</v>
       </c>
       <c r="F108" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G108" s="6" t="s">
         <v>13</v>
@@ -5643,7 +5656,7 @@
         <v>12</v>
       </c>
       <c r="F109" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G109" s="6" t="s">
         <v>13</v>
@@ -5686,15 +5699,13 @@
         <v>12</v>
       </c>
       <c r="F110" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G110" s="6" t="s">
         <v>13</v>
       </c>
       <c r="H110" s="13"/>
-      <c r="I110" s="10">
-        <v>5.0</v>
-      </c>
+      <c r="I110" s="10"/>
       <c r="J110" s="3"/>
       <c r="K110" s="3"/>
       <c r="L110" s="3"/>
@@ -5731,7 +5742,7 @@
         <v>12</v>
       </c>
       <c r="F111" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G111" s="6" t="s">
         <v>13</v>
@@ -5774,7 +5785,7 @@
         <v>12</v>
       </c>
       <c r="F112" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G112" s="6" t="s">
         <v>13</v>
@@ -5817,7 +5828,7 @@
         <v>12</v>
       </c>
       <c r="F113" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G113" s="6" t="s">
         <v>13</v>
@@ -5860,7 +5871,7 @@
         <v>12</v>
       </c>
       <c r="F114" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G114" s="6" t="s">
         <v>13</v>
@@ -5903,7 +5914,7 @@
         <v>12</v>
       </c>
       <c r="F115" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G115" s="6" t="s">
         <v>13</v>
@@ -5946,7 +5957,7 @@
         <v>12</v>
       </c>
       <c r="F116" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G116" s="6" t="s">
         <v>13</v>
@@ -5989,15 +6000,13 @@
         <v>12</v>
       </c>
       <c r="F117" s="11">
-        <v>46205.51736111111</v>
+        <v>46222.379166666666</v>
       </c>
       <c r="G117" s="6" t="s">
         <v>13</v>
       </c>
       <c r="H117" s="13"/>
-      <c r="I117" s="10">
-        <v>5.0</v>
-      </c>
+      <c r="I117" s="10"/>
       <c r="J117" s="3"/>
       <c r="K117" s="3"/>
       <c r="L117" s="3"/>
@@ -44236,10 +44245,10 @@
         <v>8</v>
       </c>
       <c r="C1890" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1890" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1891">
@@ -44250,10 +44259,10 @@
         <v>14</v>
       </c>
       <c r="C1891" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1891" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1892">
@@ -44264,10 +44273,10 @@
         <v>16</v>
       </c>
       <c r="C1892" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1892" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1893">
@@ -44278,10 +44287,10 @@
         <v>18</v>
       </c>
       <c r="C1893" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1893" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1894">
@@ -44292,10 +44301,10 @@
         <v>20</v>
       </c>
       <c r="C1894" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1894" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1895">
@@ -44306,10 +44315,10 @@
         <v>24</v>
       </c>
       <c r="C1895" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1895" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1896">
@@ -44320,10 +44329,10 @@
         <v>27</v>
       </c>
       <c r="C1896" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1896" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1897">
@@ -44334,10 +44343,10 @@
         <v>28</v>
       </c>
       <c r="C1897" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1897" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1898">
@@ -44348,10 +44357,10 @@
         <v>30</v>
       </c>
       <c r="C1898" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1898" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1899">
@@ -44362,10 +44371,10 @@
         <v>32</v>
       </c>
       <c r="C1899" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1899" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1900">
@@ -44376,10 +44385,10 @@
         <v>33</v>
       </c>
       <c r="C1900" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1900" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1901">
@@ -44390,10 +44399,10 @@
         <v>34</v>
       </c>
       <c r="C1901" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1901" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1902">
@@ -44404,10 +44413,10 @@
         <v>36</v>
       </c>
       <c r="C1902" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1902" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1903">
@@ -44418,10 +44427,10 @@
         <v>39</v>
       </c>
       <c r="C1903" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1903" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1904">
@@ -44432,10 +44441,10 @@
         <v>41</v>
       </c>
       <c r="C1904" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1904" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1905">
@@ -44446,10 +44455,10 @@
         <v>43</v>
       </c>
       <c r="C1905" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1905" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1906">
@@ -44460,10 +44469,10 @@
         <v>46</v>
       </c>
       <c r="C1906" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1906" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1907">
@@ -44474,10 +44483,10 @@
         <v>47</v>
       </c>
       <c r="C1907" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1907" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1908">
@@ -44488,10 +44497,10 @@
         <v>48</v>
       </c>
       <c r="C1908" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1908" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1909">
@@ -44502,10 +44511,10 @@
         <v>49</v>
       </c>
       <c r="C1909" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1909" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1910">
@@ -44516,10 +44525,10 @@
         <v>50</v>
       </c>
       <c r="C1910" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1910" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1911">
@@ -44530,10 +44539,10 @@
         <v>51</v>
       </c>
       <c r="C1911" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1911" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1912">
@@ -44544,10 +44553,10 @@
         <v>53</v>
       </c>
       <c r="C1912" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1912" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1913">
@@ -44558,10 +44567,10 @@
         <v>54</v>
       </c>
       <c r="C1913" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1913" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1914">
@@ -44572,10 +44581,10 @@
         <v>56</v>
       </c>
       <c r="C1914" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1914" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1915">
@@ -44586,10 +44595,10 @@
         <v>57</v>
       </c>
       <c r="C1915" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1915" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1916">
@@ -44600,10 +44609,10 @@
         <v>58</v>
       </c>
       <c r="C1916" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1916" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1917">
@@ -44614,10 +44623,10 @@
         <v>59</v>
       </c>
       <c r="C1917" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1917" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1918">
@@ -44628,10 +44637,10 @@
         <v>60</v>
       </c>
       <c r="C1918" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1918" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1919">
@@ -44642,10 +44651,10 @@
         <v>61</v>
       </c>
       <c r="C1919" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1919" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1920">
@@ -44656,10 +44665,10 @@
         <v>62</v>
       </c>
       <c r="C1920" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1920" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1921">
@@ -44670,10 +44679,10 @@
         <v>63</v>
       </c>
       <c r="C1921" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1921" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1922">
@@ -44684,10 +44693,10 @@
         <v>64</v>
       </c>
       <c r="C1922" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1922" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1923">
@@ -44698,10 +44707,10 @@
         <v>65</v>
       </c>
       <c r="C1923" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1923" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1924">
@@ -44712,10 +44721,10 @@
         <v>66</v>
       </c>
       <c r="C1924" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1924" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1925">
@@ -44726,10 +44735,10 @@
         <v>67</v>
       </c>
       <c r="C1925" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1925" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1926">
@@ -44740,10 +44749,10 @@
         <v>68</v>
       </c>
       <c r="C1926" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1926" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1927">
@@ -44754,10 +44763,10 @@
         <v>70</v>
       </c>
       <c r="C1927" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1927" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1928">
@@ -44768,10 +44777,10 @@
         <v>71</v>
       </c>
       <c r="C1928" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1928" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1929">
@@ -44782,10 +44791,10 @@
         <v>72</v>
       </c>
       <c r="C1929" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1929" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1930">
@@ -44796,10 +44805,10 @@
         <v>73</v>
       </c>
       <c r="C1930" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1930" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1931">
@@ -44810,10 +44819,10 @@
         <v>74</v>
       </c>
       <c r="C1931" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1931" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1932">
@@ -44824,10 +44833,10 @@
         <v>75</v>
       </c>
       <c r="C1932" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1932" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1933">
@@ -44838,10 +44847,10 @@
         <v>77</v>
       </c>
       <c r="C1933" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1933" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1934">
@@ -44852,10 +44861,10 @@
         <v>79</v>
       </c>
       <c r="C1934" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1934" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1935">
@@ -44866,10 +44875,10 @@
         <v>81</v>
       </c>
       <c r="C1935" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1935" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1936">
@@ -44880,10 +44889,10 @@
         <v>82</v>
       </c>
       <c r="C1936" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1936" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1937">
@@ -44894,10 +44903,10 @@
         <v>83</v>
       </c>
       <c r="C1937" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1937" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1938">
@@ -44908,10 +44917,10 @@
         <v>84</v>
       </c>
       <c r="C1938" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1938" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1939">
@@ -44922,10 +44931,10 @@
         <v>85</v>
       </c>
       <c r="C1939" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1939" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1940">
@@ -44936,10 +44945,10 @@
         <v>86</v>
       </c>
       <c r="C1940" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1940" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1941">
@@ -44950,10 +44959,10 @@
         <v>87</v>
       </c>
       <c r="C1941" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1941" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1942">
@@ -44964,10 +44973,10 @@
         <v>88</v>
       </c>
       <c r="C1942" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1942" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1943">
@@ -44978,10 +44987,10 @@
         <v>89</v>
       </c>
       <c r="C1943" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1943" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1944">
@@ -44992,10 +45001,10 @@
         <v>90</v>
       </c>
       <c r="C1944" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1944" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1945">
@@ -45006,10 +45015,10 @@
         <v>91</v>
       </c>
       <c r="C1945" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1945" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1946">
@@ -45020,10 +45029,10 @@
         <v>92</v>
       </c>
       <c r="C1946" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1946" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1947">
@@ -45034,10 +45043,10 @@
         <v>93</v>
       </c>
       <c r="C1947" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1947" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1948">
@@ -45048,10 +45057,10 @@
         <v>94</v>
       </c>
       <c r="C1948" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1948" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1949">
@@ -45062,10 +45071,10 @@
         <v>95</v>
       </c>
       <c r="C1949" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1949" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1950">
@@ -45076,10 +45085,10 @@
         <v>97</v>
       </c>
       <c r="C1950" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1950" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1951">
@@ -45090,10 +45099,10 @@
         <v>99</v>
       </c>
       <c r="C1951" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1951" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1952">
@@ -45104,10 +45113,10 @@
         <v>100</v>
       </c>
       <c r="C1952" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1952" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1953">
@@ -45118,10 +45127,10 @@
         <v>102</v>
       </c>
       <c r="C1953" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1953" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1954">
@@ -45132,10 +45141,10 @@
         <v>103</v>
       </c>
       <c r="C1954" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1954" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1955">
@@ -45146,10 +45155,10 @@
         <v>104</v>
       </c>
       <c r="C1955" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1955" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1956">
@@ -45160,10 +45169,10 @@
         <v>106</v>
       </c>
       <c r="C1956" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1956" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1957">
@@ -45174,10 +45183,10 @@
         <v>107</v>
       </c>
       <c r="C1957" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1957" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1958">
@@ -45188,10 +45197,10 @@
         <v>108</v>
       </c>
       <c r="C1958" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1958" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1959">
@@ -45202,10 +45211,10 @@
         <v>109</v>
       </c>
       <c r="C1959" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1959" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1960">
@@ -45216,10 +45225,10 @@
         <v>110</v>
       </c>
       <c r="C1960" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1960" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1961">
@@ -45230,10 +45239,10 @@
         <v>111</v>
       </c>
       <c r="C1961" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1961" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1962">
@@ -45244,10 +45253,10 @@
         <v>112</v>
       </c>
       <c r="C1962" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1962" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1963">
@@ -45258,10 +45267,10 @@
         <v>113</v>
       </c>
       <c r="C1963" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1963" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1964">
@@ -45272,10 +45281,10 @@
         <v>114</v>
       </c>
       <c r="C1964" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1964" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1965">
@@ -45286,10 +45295,10 @@
         <v>115</v>
       </c>
       <c r="C1965" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1965" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1966">
@@ -45300,10 +45309,10 @@
         <v>116</v>
       </c>
       <c r="C1966" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1966" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1967">
@@ -45314,10 +45323,10 @@
         <v>117</v>
       </c>
       <c r="C1967" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1967" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1968">
@@ -45328,10 +45337,10 @@
         <v>118</v>
       </c>
       <c r="C1968" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1968" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1969">
@@ -45342,10 +45351,10 @@
         <v>119</v>
       </c>
       <c r="C1969" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1969" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1970">
@@ -45356,10 +45365,10 @@
         <v>120</v>
       </c>
       <c r="C1970" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1970" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1971">
@@ -45370,10 +45379,10 @@
         <v>121</v>
       </c>
       <c r="C1971" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1971" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1972">
@@ -45384,10 +45393,10 @@
         <v>122</v>
       </c>
       <c r="C1972" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1972" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1973">
@@ -45398,10 +45407,10 @@
         <v>124</v>
       </c>
       <c r="C1973" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1973" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1974">
@@ -45412,10 +45421,10 @@
         <v>125</v>
       </c>
       <c r="C1974" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1974" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1975">
@@ -45426,10 +45435,10 @@
         <v>126</v>
       </c>
       <c r="C1975" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1975" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1976">
@@ -45440,10 +45449,10 @@
         <v>127</v>
       </c>
       <c r="C1976" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1976" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1977">
@@ -45454,10 +45463,10 @@
         <v>129</v>
       </c>
       <c r="C1977" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1977" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1978">
@@ -45468,10 +45477,10 @@
         <v>131</v>
       </c>
       <c r="C1978" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1978" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1979">
@@ -45482,10 +45491,10 @@
         <v>133</v>
       </c>
       <c r="C1979" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1979" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1980">
@@ -45496,10 +45505,10 @@
         <v>134</v>
       </c>
       <c r="C1980" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1980" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1981">
@@ -45510,10 +45519,10 @@
         <v>135</v>
       </c>
       <c r="C1981" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1981" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1982">
@@ -45524,10 +45533,10 @@
         <v>136</v>
       </c>
       <c r="C1982" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1982" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1983">
@@ -45538,10 +45547,10 @@
         <v>137</v>
       </c>
       <c r="C1983" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1983" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1984">
@@ -45552,10 +45561,10 @@
         <v>138</v>
       </c>
       <c r="C1984" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1984" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1985">
@@ -45566,10 +45575,10 @@
         <v>139</v>
       </c>
       <c r="C1985" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1985" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1986">
@@ -45580,10 +45589,10 @@
         <v>140</v>
       </c>
       <c r="C1986" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1986" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1987">
@@ -45594,10 +45603,10 @@
         <v>141</v>
       </c>
       <c r="C1987" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1987" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1988">
@@ -45608,10 +45617,10 @@
         <v>142</v>
       </c>
       <c r="C1988" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1988" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1989">
@@ -45622,10 +45631,10 @@
         <v>143</v>
       </c>
       <c r="C1989" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1989" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1990">
@@ -45636,10 +45645,10 @@
         <v>144</v>
       </c>
       <c r="C1990" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1990" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1991">
@@ -45650,10 +45659,10 @@
         <v>145</v>
       </c>
       <c r="C1991" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1991" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1992">
@@ -45664,10 +45673,10 @@
         <v>146</v>
       </c>
       <c r="C1992" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1992" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1993">
@@ -45678,10 +45687,10 @@
         <v>147</v>
       </c>
       <c r="C1993" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1993" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1994">
@@ -45692,10 +45701,10 @@
         <v>148</v>
       </c>
       <c r="C1994" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1994" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1995">
@@ -45706,10 +45715,10 @@
         <v>149</v>
       </c>
       <c r="C1995" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1995" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1996">
@@ -45720,10 +45729,10 @@
         <v>150</v>
       </c>
       <c r="C1996" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1996" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1997">
@@ -45734,10 +45743,10 @@
         <v>151</v>
       </c>
       <c r="C1997" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1997" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1998">
@@ -45748,10 +45757,10 @@
         <v>152</v>
       </c>
       <c r="C1998" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1998" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1999">
@@ -45762,10 +45771,10 @@
         <v>153</v>
       </c>
       <c r="C1999" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D1999" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2000">
@@ -45776,10 +45785,10 @@
         <v>154</v>
       </c>
       <c r="C2000" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D2000" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2001">
@@ -45790,10 +45799,10 @@
         <v>155</v>
       </c>
       <c r="C2001" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D2001" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2002">
@@ -45804,10 +45813,10 @@
         <v>156</v>
       </c>
       <c r="C2002" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D2002" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2003">
@@ -45818,10 +45827,10 @@
         <v>157</v>
       </c>
       <c r="C2003" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D2003" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2004">
@@ -45832,10 +45841,10 @@
         <v>158</v>
       </c>
       <c r="C2004" s="18" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="D2004" s="18" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2005">
@@ -45846,68 +45855,2013 @@
         <v>159</v>
       </c>
       <c r="C2005" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="D2005" s="18" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" s="17">
+        <v>46207.71944444445</v>
+      </c>
+      <c r="B2006" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2006" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D2005" s="18" t="s">
+      <c r="D2006" s="18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2006">
-      <c r="A2006" s="17"/>
-    </row>
     <row r="2007">
-      <c r="A2007" s="17"/>
+      <c r="A2007" s="17">
+        <v>46207.71944444445</v>
+      </c>
+      <c r="B2007" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2007" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2007" s="18" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2008">
-      <c r="A2008" s="17"/>
+      <c r="A2008" s="17">
+        <v>46207.71944444445</v>
+      </c>
+      <c r="B2008" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2008" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2008" s="18" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2009">
-      <c r="A2009" s="17"/>
+      <c r="A2009" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2009" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2009" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2009" s="18" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2010">
-      <c r="A2010" s="17"/>
+      <c r="A2010" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2010" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2010" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2010" s="18" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2011">
-      <c r="A2011" s="17"/>
+      <c r="A2011" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2011" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2011" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2011" s="18" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2012">
-      <c r="A2012" s="17"/>
+      <c r="A2012" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2012" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2012" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2012" s="18" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2013">
-      <c r="A2013" s="17"/>
+      <c r="A2013" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2013" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2013" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2013" s="18" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2014">
-      <c r="A2014" s="17"/>
+      <c r="A2014" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2014" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2014" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2014" s="18" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2015">
-      <c r="A2015" s="17"/>
+      <c r="A2015" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2015" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2015" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2015" s="18" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2016">
-      <c r="A2016" s="17"/>
+      <c r="A2016" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2016" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2016" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2016" s="18" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2017">
-      <c r="A2017" s="17"/>
+      <c r="A2017" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2017" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2017" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2017" s="18" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2018">
-      <c r="A2018" s="17"/>
+      <c r="A2018" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2018" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2018" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2018" s="18" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2019">
-      <c r="A2019" s="17"/>
+      <c r="A2019" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2019" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2019" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2019" s="18" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2020">
-      <c r="A2020" s="17"/>
+      <c r="A2020" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2020" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2020" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2020" s="18" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2021">
-      <c r="A2021" s="17"/>
+      <c r="A2021" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2021" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2021" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2021" s="18" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2022">
-      <c r="A2022" s="17"/>
+      <c r="A2022" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2022" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2022" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2022" s="18" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2023">
-      <c r="A2023" s="17"/>
+      <c r="A2023" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2023" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2023" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2023" s="18" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2024">
-      <c r="A2024" s="17"/>
+      <c r="A2024" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2024" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2024" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2024" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2025" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2025" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2025" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2026" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2026" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2026" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2027" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2027" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2027" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2028" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2028" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2028" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2029" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2029" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2029" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2030" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2030" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2030" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2031" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2031" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2031" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" s="17">
+        <v>46222.37847222222</v>
+      </c>
+      <c r="B2032" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2032" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2032" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2033" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2033" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2033" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2034" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2034" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2034" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2035" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2035" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2035" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2036" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2036" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2036" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2037" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2037" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2037" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2038" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2038" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2038" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2039" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2039" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2039" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2040" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2040" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2040" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2041" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2041" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2041" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2042" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2042" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2042" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2043" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2043" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2043" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2044" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2044" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2044" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2045" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2045" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2045" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2046" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2046" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2046" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2047" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2047" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2047" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2048" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2048" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2048" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2049" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2049" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2049" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2050" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2050" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2050" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2051" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2051" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2051" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2052" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2052" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2052" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2053" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2053" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2053" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2054" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2054" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2054" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2055" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2055" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2055" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2056" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2056" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2056" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2057" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2057" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2057" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2058" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2058" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2058" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2059" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2059" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2059" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2060" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2060" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2060" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2061" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2061" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2061" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2062" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2062" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2062" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2063" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2063" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2063" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2064" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2064" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2064" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2065" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2065" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2065" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2066" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2066" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2066" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2067" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2067" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2067" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2068" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2068" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2068" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2069" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2069" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2069" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2070" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2070" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2070" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2071" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2071" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2071" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2072" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2072" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2072" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2073" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2073" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2073" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2074" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2074" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2074" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2075" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2075" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2075" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2076" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2076" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2076" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2077" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2077" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2077" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2078" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2078" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2078" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2079" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2079" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2079" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2080" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2080" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2080" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2081" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2081" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2081" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2082" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2082" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2082" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2083" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2083" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2083" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2084" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2084" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2084" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2085" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2085" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2085" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2086" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2086" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2086" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2087" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2087" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2087" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2088" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2088" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2088" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2089" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2089" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2089" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2090" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2090" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2090" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2091" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2091" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2091" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2092" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2092" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2092" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2093" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2093" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2093" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2094" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2094" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2094" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2095" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2095" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2095" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2096" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2096" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2096" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2097" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2097" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2097" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2098" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2098" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2098" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2099" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2099" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2099" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2100" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2100" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2100" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2101" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2101" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2101" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2102" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2102" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2102" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2103" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2103" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2103" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2104" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2104" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2104" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2105" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2105" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2105" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2106" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2106" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2106" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2107" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2107" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2107" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2108" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2108" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2108" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2109" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2109" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2109" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2110" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2110" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2110" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2111" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2111" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2111" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2112" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2112" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2112" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2113" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2113" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2113" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2114" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2114" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2114" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2115" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2115" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2115" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2116" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2116" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2116" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2117" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2117" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2117" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2118" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2118" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2118" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2119" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="C2119" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2119" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2120" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2120" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2120" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2121" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2121" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2121" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2122" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2122" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2122" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2123" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2123" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2123" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2124" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2124" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2124" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2125" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2125" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2125" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2126" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2126" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2126" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2127" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2127" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2127" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2128" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2128" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2128" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2129" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2129" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2129" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2130" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="C2130" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2130" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2131" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2131" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2131" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2132" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2132" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2132" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2133" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2133" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2133" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2134" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2134" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2134" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2135" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="C2135" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2135" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2136" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="C2136" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2136" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2137" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2137" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2137" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2138" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2138" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2138" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2139" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2139" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2139" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2140" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2140" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2140" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2141" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2141" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2141" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2142" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="C2142" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2142" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2143" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2143" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2143" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2144" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="C2144" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2144" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2145" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="C2145" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2145" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2146" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2146" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2146" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2147" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2147" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2147" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" s="17">
+        <v>46222.379166666666</v>
+      </c>
+      <c r="B2148" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2148" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2148" s="18" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -45923,25 +47877,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>160</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2">
@@ -45970,400 +47924,363 @@
         <v>0</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F1" s="18" t="s">
         <v>161</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="21">
-        <v>46218.56127907407</v>
+        <v>46218.72193804398</v>
       </c>
       <c r="B2" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D2" s="22">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G2" s="18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="21">
-        <v>46218.56202780093</v>
+        <v>46218.72193804398</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C3" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="D3" s="22">
+        <v>4.0</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="F3" s="23" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="22">
-        <v>-5.0</v>
-      </c>
-      <c r="E3" s="18" t="s">
+      <c r="G3" s="18" t="s">
         <v>177</v>
-      </c>
-      <c r="F3" s="23" t="s">
-        <v>178</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="21">
-        <v>46218.57821987268</v>
+        <v>46218.72275060185</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D4" s="22">
-        <v>10.0</v>
+        <v>-3.0</v>
       </c>
       <c r="E4" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="F4" s="23" t="s">
-        <v>180</v>
-      </c>
       <c r="G4" s="18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="21">
-        <v>46218.58194193287</v>
+        <v>46218.72275060185</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D5" s="22">
-        <v>7.0</v>
+        <v>-3.0</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21">
-        <v>46096.69338135417</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="D6" s="22">
-        <v>5.0</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>175</v>
-      </c>
+      <c r="A6" s="21"/>
     </row>
     <row r="7">
-      <c r="A7" s="21">
-        <v>46096.69338135417</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="D7" s="22">
-        <v>5.0</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>175</v>
-      </c>
+      <c r="A7" s="21"/>
     </row>
     <row r="8">
-      <c r="A8" s="21">
-        <v>46096.69338135417</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="D8" s="22">
-        <v>5.0</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>175</v>
-      </c>
+      <c r="A8" s="21"/>
     </row>
     <row r="9">
-      <c r="A9" s="21">
-        <v>46096.69338135417</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="D9" s="22">
-        <v>5.0</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>175</v>
-      </c>
+      <c r="A9" s="21"/>
     </row>
     <row r="10">
-      <c r="A10" s="21">
-        <v>46096.69338135417</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="D10" s="22">
-        <v>5.0</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>175</v>
-      </c>
+      <c r="A10" s="21"/>
     </row>
     <row r="11">
-      <c r="A11" s="21">
-        <v>46096.69338135417</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="D11" s="22">
-        <v>5.0</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>175</v>
-      </c>
+      <c r="A11" s="21"/>
     </row>
     <row r="12">
-      <c r="A12" s="21">
-        <v>46096.69338135417</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="D12" s="22">
-        <v>5.0</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>175</v>
-      </c>
+      <c r="A12" s="21"/>
     </row>
     <row r="13">
-      <c r="A13" s="21">
-        <v>46096.69338135417</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="D13" s="22">
-        <v>5.0</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>175</v>
-      </c>
+      <c r="A13" s="21"/>
     </row>
     <row r="14">
-      <c r="A14" s="21">
-        <v>46096.69338135417</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="D14" s="22">
-        <v>5.0</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>175</v>
-      </c>
+      <c r="A14" s="21"/>
     </row>
     <row r="15">
-      <c r="A15" s="21">
-        <v>46096.69338135417</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="D15" s="22">
-        <v>5.0</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>175</v>
-      </c>
+      <c r="A15" s="21"/>
     </row>
     <row r="16">
-      <c r="A16" s="21">
-        <v>46096.69338135417</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="D16" s="22">
-        <v>5.0</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>175</v>
-      </c>
+      <c r="A16" s="21"/>
     </row>
     <row r="17">
-      <c r="A17" s="21">
-        <v>46096.69338135417</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="D17" s="22">
-        <v>5.0</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>175</v>
-      </c>
+      <c r="A17" s="21"/>
     </row>
     <row r="18">
-      <c r="A18" s="21">
-        <v>46096.69338135417</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="D18" s="22">
-        <v>5.0</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>175</v>
-      </c>
+      <c r="A18" s="21"/>
     </row>
     <row r="19">
-      <c r="A19" s="21">
-        <v>46096.69338135417</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="D19" s="22">
-        <v>5.0</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>175</v>
-      </c>
+      <c r="A19" s="21"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="F2"/>
     <hyperlink r:id="rId2" ref="F3"/>
-    <hyperlink r:id="rId3" ref="F4"/>
-    <hyperlink r:id="rId4" ref="F5"/>
   </hyperlinks>
-  <drawing r:id="rId5"/>
+  <drawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="s">
+        <v>130</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="s">
+        <v>191</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>